--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45971.41666666666</v>
+        <v>45971.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45971.4375</v>
+        <v>45971.5625</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45971.5625</v>
+        <v>45971.625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45971.625</v>
+        <v>45971.6875</v>
       </c>
     </row>
     <row r="12">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,264 +2167,6 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45971.6875</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
-        <v>45971.79166666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
         <v>45971.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45971.4375</v>
+        <v>45971.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45971.5625</v>
+        <v>45971.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45971.625</v>
+        <v>45971.5625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45971.6875</v>
+        <v>45971.625</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2047,126 +2047,255 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45971.6875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>2.06</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N14" t="n">
         <v>3.55</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2.38</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z14" t="n">
         <v>1.47</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45971.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2168,135 +2168,6 @@
       </c>
       <c r="AK13" s="3" t="n">
         <v>45971.6875</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
-        <v>45971.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2168,6 +2168,264 @@
       </c>
       <c r="AK13" s="3" t="n">
         <v>45971.6875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45971.79166666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45971.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.21</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2296,135 +2296,6 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45971.79166666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
         <v>45971.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2176,126 +2176,255 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45971.79166666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>2.06</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N15" t="n">
         <v>3.55</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z15" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45971.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45971.79166666666</v>
+        <v>45971.75</v>
       </c>
     </row>
     <row r="15">

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45971.38541666666</v>
+        <v>45971.375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45971.41666666666</v>
+        <v>45971.38541666666</v>
       </c>
     </row>
     <row r="7">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45971.4375</v>
+        <v>45971.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45971.5625</v>
+        <v>45971.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45971.625</v>
+        <v>45971.5625</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45971.6875</v>
+        <v>45971.625</v>
       </c>
     </row>
     <row r="13">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>4.21</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45971.75</v>
+        <v>45971.6875</v>
       </c>
     </row>
     <row r="15">
@@ -2305,126 +2305,255 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45971.79166666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>2.06</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>3.55</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z16" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
         <v>45971.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,115 +508,60 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>homeGoals</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -710,44 +655,7 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="3" t="n">
+      <c r="Z2" s="3" t="n">
         <v>45971.33333333334</v>
       </c>
     </row>
@@ -839,44 +747,7 @@
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="3" t="n">
+      <c r="Z3" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -968,44 +839,7 @@
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="3" t="n">
+      <c r="Z4" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -1097,44 +931,7 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="3" t="n">
+      <c r="Z5" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -1226,44 +1023,7 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
+      <c r="Z6" s="3" t="n">
         <v>45971.38541666666</v>
       </c>
     </row>
@@ -1355,44 +1115,7 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3" t="n">
+      <c r="Z7" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1484,44 +1207,7 @@
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
+      <c r="Z8" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1613,44 +1299,7 @@
       <c r="Y9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="n">
+      <c r="Z9" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1742,44 +1391,7 @@
       <c r="Y10" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>45971.4375</v>
       </c>
     </row>
@@ -1863,52 +1475,15 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="n">
+      <c r="Z11" s="3" t="n">
         <v>45971.5625</v>
       </c>
     </row>
@@ -2000,44 +1575,7 @@
       <c r="Y12" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3" t="n">
+      <c r="Z12" s="3" t="n">
         <v>45971.625</v>
       </c>
     </row>
@@ -2106,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -2127,46 +1665,9 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3" t="n">
         <v>45971.6875</v>
       </c>
     </row>
@@ -2235,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2256,46 +1757,9 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="n">
         <v>45971.6875</v>
       </c>
     </row>
@@ -2355,76 +1819,39 @@
         <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.25</v>
+        <v>1.33</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>1.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>1.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3" t="n">
         <v>45971.79166666666</v>
       </c>
     </row>
@@ -2493,10 +1920,10 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2514,46 +1941,9 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="3" t="n">
         <v>45971.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,60 +508,75 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Odd_H_HT</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_HT</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_H</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_A</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -655,7 +670,16 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3" t="n">
         <v>45971.33333333334</v>
       </c>
     </row>
@@ -747,7 +771,16 @@
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -839,7 +872,16 @@
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="3" t="n">
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -931,7 +973,16 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -1023,7 +1074,16 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3" t="n">
         <v>45971.38541666666</v>
       </c>
     </row>
@@ -1115,7 +1175,16 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1207,7 +1276,16 @@
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1299,7 +1377,16 @@
       <c r="Y9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="3" t="n">
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1391,7 +1478,16 @@
       <c r="Y10" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="3" t="n">
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3" t="n">
         <v>45971.4375</v>
       </c>
     </row>
@@ -1483,7 +1579,16 @@
       <c r="Y11" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3" t="n">
         <v>45971.5625</v>
       </c>
     </row>
@@ -1575,7 +1680,16 @@
       <c r="Y12" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3" t="n">
         <v>45971.625</v>
       </c>
     </row>
@@ -1644,20 +1758,20 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>1.65</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
@@ -1667,7 +1781,16 @@
       <c r="Y13" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3" t="n">
         <v>45971.6875</v>
       </c>
     </row>
@@ -1736,20 +1859,20 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.98</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>1.77</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
@@ -1759,7 +1882,16 @@
       <c r="Y14" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="n">
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="n">
         <v>45971.6875</v>
       </c>
     </row>
@@ -1819,39 +1951,48 @@
         <v>3.45</v>
       </c>
       <c r="O15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.42</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>1.33</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>2.1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>1.65</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>1.85</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>1.85</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>1.26</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
         <v>1.76</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="n">
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="n">
         <v>45971.79166666666</v>
       </c>
     </row>
@@ -1920,20 +2061,20 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.4</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>1.48</v>
       </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
@@ -1943,7 +2084,16 @@
       <c r="Y16" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="3" t="n">
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3" t="n">
         <v>45971.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2094,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>45971.89583333334</v>
+        <v>45971.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1547,40 +1547,40 @@
         <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1648,40 +1648,40 @@
         <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.76</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
         <v>2.81</v>
@@ -1262,10 +1262,10 @@
         <v>1.22</v>
       </c>
       <c r="U8" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
         <v>2.15</v>
@@ -1274,10 +1274,10 @@
         <v>1.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1547,13 +1547,13 @@
         <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.33</v>
+        <v>4.95</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
@@ -1565,22 +1565,22 @@
         <v>1.25</v>
       </c>
       <c r="U11" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="V11" t="n">
         <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.61</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1639,34 +1639,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
         <v>2.25</v>
@@ -1675,13 +1675,13 @@
         <v>1.48</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,49 +1740,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,49 +1336,49 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,49 +1740,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="P13" t="n">
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.48</v>
+        <v>3.79</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.79</v>
+        <v>3.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -629,22 +629,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -674,13 +674,13 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>45971.33333333334</v>
+        <v>45971.25</v>
       </c>
     </row>
     <row r="3">
@@ -689,12 +689,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>45971.375</v>
+        <v>45971.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>45971.38541666666</v>
+        <v>45971.375</v>
       </c>
     </row>
     <row r="7">
@@ -1093,27 +1093,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>45971.41666666666</v>
+        <v>45971.38541666666</v>
       </c>
     </row>
     <row r="8">
@@ -1345,7 +1345,7 @@
         <v>4.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
         <v>1.86</v>
@@ -1363,22 +1363,22 @@
         <v>1.22</v>
       </c>
       <c r="U9" t="n">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="X9" t="n">
         <v>1.63</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1396,27 +1396,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>45971.4375</v>
+        <v>45971.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1538,49 +1538,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>45971.5625</v>
+        <v>45971.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1598,27 +1598,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1639,49 +1639,49 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.45</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.02</v>
-      </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.52</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2.25</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>2.36</v>
+        <v>1.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>45971.625</v>
+        <v>45971.5625</v>
       </c>
     </row>
     <row r="13">
@@ -1699,27 +1699,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,49 +1740,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.79</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="T13" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>45971.6875</v>
+        <v>45971.625</v>
       </c>
     </row>
     <row r="14">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="P14" t="n">
         <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1901,27 +1901,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,50 +1942,50 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.95</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.48</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>45971.79166666666</v>
+        <v>45971.6875</v>
       </c>
     </row>
     <row r="16">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,57 +2043,158 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
         <v>2.02</v>
       </c>
       <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3" t="n">
+        <v>45971.79166666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4.58</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>1.43</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>3.05</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>1.32</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>2.1</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V17" t="n">
         <v>1.65</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W17" t="n">
         <v>1.87</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X17" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y17" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z17" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="3" t="n">
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3" t="n">
         <v>45971.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="N2" t="n">
         <v>1.92</v>
@@ -647,13 +647,13 @@
         <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U2" t="n">
         <v>1.85</v>
@@ -668,10 +668,10 @@
         <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA2" t="n">
         <v>2.37</v>
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,49 +1336,49 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1598,27 +1598,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1639,49 +1639,49 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>2.47</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>2.65</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>45971.5625</v>
+        <v>45971.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -1699,27 +1699,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,49 +1740,49 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.5</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="V13" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
-        <v>2.36</v>
+        <v>1.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.43</v>
+        <v>1.94</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>45971.625</v>
+        <v>45971.5625</v>
       </c>
     </row>
     <row r="14">
@@ -1800,27 +1800,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.62</v>
+        <v>2.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="T14" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>45971.6875</v>
+        <v>45971.625</v>
       </c>
     </row>
     <row r="15">
@@ -1945,46 +1945,46 @@
         <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
         <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2002,27 +2002,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="T16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="X16" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>45971.79166666666</v>
+        <v>45971.6875</v>
       </c>
     </row>
     <row r="17">
@@ -2118,83 +2118,184 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3" t="n">
+        <v>45971.79166666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>1.97</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>3.09</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>3.45</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O18" t="n">
         <v>2.5</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P18" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="Q18" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.43</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>3.05</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>1.32</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>2.1</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V18" t="n">
         <v>1.65</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W18" t="n">
         <v>1.87</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X18" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y18" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z18" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="3" t="n">
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3" t="n">
         <v>45971.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -629,58 +629,58 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>45971.25</v>
+        <v>45971.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -689,12 +689,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>45971.33333333334</v>
+        <v>45971.375</v>
       </c>
     </row>
     <row r="4">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>45971.375</v>
+        <v>45971.38541666666</v>
       </c>
     </row>
     <row r="7">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,49 +1134,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>45971.38541666666</v>
+        <v>45971.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1396,27 +1396,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>45971.41666666666</v>
+        <v>45971.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1497,27 +1497,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1538,49 +1538,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>45971.4375</v>
+        <v>45971.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1598,27 +1598,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1639,49 +1639,49 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="N12" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>2.48</v>
       </c>
       <c r="V12" t="n">
-        <v>2.65</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>2.44</v>
+        <v>1.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>45971.45833333334</v>
+        <v>45971.5625</v>
       </c>
     </row>
     <row r="13">
@@ -1699,27 +1699,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,49 +1740,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.16</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>4.45</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.2</v>
+        <v>2.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>2.48</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.94</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>45971.5625</v>
+        <v>45971.625</v>
       </c>
     </row>
     <row r="14">
@@ -1800,27 +1800,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,50 +1841,50 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.85</v>
+        <v>3.98</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.29</v>
+        <v>2.86</v>
       </c>
       <c r="T14" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.57</v>
       </c>
-      <c r="V14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>45971.625</v>
+        <v>45971.6875</v>
       </c>
     </row>
     <row r="15">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,58 +2043,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>3.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.49</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.98</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.42</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="V16" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>45971.6875</v>
+        <v>45971.70833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2144,49 +2144,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.31</v>
+        <v>4.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="W17" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="X17" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2245,49 +2245,49 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="P18" t="n">
         <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="T18" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1538,43 +1538,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.57</v>
       </c>
       <c r="N11" t="n">
-        <v>4.65</v>
+        <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.18</v>
+        <v>4.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U11" t="n">
         <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="W11" t="n">
         <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
         <v>1.16</v>
@@ -1749,13 +1749,13 @@
         <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -1764,7 +1764,7 @@
         <v>2.29</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="U13" t="n">
         <v>1.57</v>
@@ -1779,10 +1779,10 @@
         <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
         <v>3.98</v>
@@ -1868,22 +1868,22 @@
         <v>1.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
         <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1957,31 +1957,31 @@
         <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
         <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
         <v>1.46</v>
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>2.75</v>
@@ -2168,7 +2168,7 @@
         <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="U17" t="n">
         <v>2.16</v>
@@ -2180,7 +2180,7 @@
         <v>1.88</v>
       </c>
       <c r="X17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Y17" t="n">
         <v>1.21</v>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
@@ -2272,13 +2272,13 @@
         <v>1.29</v>
       </c>
       <c r="U18" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
         <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.68</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>4.15</v>
       </c>
       <c r="O7" t="n">
         <v>2.92</v>
@@ -1149,7 +1149,7 @@
         <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.56</v>
@@ -1161,7 +1161,7 @@
         <v>1.22</v>
       </c>
       <c r="U7" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4.99</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
         <v>2.05</v>
@@ -1556,25 +1556,25 @@
         <v>4.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="T11" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="W11" t="n">
         <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
         <v>1.16</v>
@@ -1639,25 +1639,25 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="P12" t="n">
         <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
         <v>3.5</v>
@@ -1672,10 +1672,10 @@
         <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="X12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Y12" t="n">
         <v>1.32</v>
@@ -1749,28 +1749,28 @@
         <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="T13" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="U13" t="n">
         <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.48</v>
@@ -1779,10 +1779,10 @@
         <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1850,22 +1850,22 @@
         <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.98</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
@@ -1877,13 +1877,13 @@
         <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1942,25 +1942,25 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N15" t="n">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>3.04</v>
@@ -1969,22 +1969,22 @@
         <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W15" t="n">
         <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="M16" t="n">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
       <c r="N16" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="O16" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="P16" t="n">
         <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="V16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.95</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA16" t="n">
         <v>2.37</v>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2144,49 +2144,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.58</v>
+        <v>3.77</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="T17" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2245,49 +2245,49 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.42</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W18" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="X18" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,49 +1134,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.92</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M15" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.13</v>
+        <v>4.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,49 +1134,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1749,22 +1749,22 @@
         <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="T13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
         <v>1.57</v>
@@ -1779,7 +1779,7 @@
         <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
         <v>1.43</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.13</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
         <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>3.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="T15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,49 +1134,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,49 +1336,49 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1437,49 +1437,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -1556,31 +1556,31 @@
         <v>4.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
         <v>2.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1639,49 +1639,49 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.25</v>
+        <v>5.53</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="U12" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="X12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1749,7 +1749,7 @@
         <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
         <v>2.26</v>
@@ -1761,7 +1761,7 @@
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.51</v>
@@ -1779,7 +1779,7 @@
         <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
         <v>1.43</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="X14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2043,34 +2043,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="N16" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="O16" t="n">
-        <v>4.39</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
         <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V16" t="n">
         <v>1.88</v>
@@ -2079,10 +2079,10 @@
         <v>1.74</v>
       </c>
       <c r="X16" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
         <v>1.22</v>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2144,49 +2144,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.77</v>
+        <v>4.61</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="X17" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2245,49 +2245,49 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="M18" t="n">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.61</v>
+        <v>3.77</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="T18" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,49 +1336,49 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1497,27 +1497,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1538,49 +1538,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>2.97</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.35</v>
+        <v>5.53</v>
       </c>
       <c r="R11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.21</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.68</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>2.65</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.53</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>2.58</v>
+        <v>1.57</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>45971.45833333334</v>
+        <v>45971.5625</v>
       </c>
     </row>
     <row r="12">
@@ -1598,27 +1598,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1639,49 +1639,49 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.97</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.53</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>3.68</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.21</v>
       </c>
-      <c r="U12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z12" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>45971.5625</v>
+        <v>45971.625</v>
       </c>
     </row>
     <row r="13">
@@ -1699,27 +1699,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1743,46 +1743,46 @@
         <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>45971.625</v>
+        <v>45971.6875</v>
       </c>
     </row>
     <row r="14">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
         <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="T14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,58 +1942,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="O15" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="W15" t="n">
         <v>1.74</v>
       </c>
       <c r="X15" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>45971.6875</v>
+        <v>45971.70833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2002,27 +2002,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,58 +2043,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.88</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>45971.70833333334</v>
+        <v>45971.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2144,22 +2144,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="P17" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
@@ -2168,25 +2168,25 @@
         <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W17" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="X17" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2195,107 +2195,6 @@
         <v>0</v>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>45971.79166666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="3" t="n">
         <v>45971.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,49 +1134,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,49 +1235,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>2.19</v>
@@ -1464,10 +1464,10 @@
         <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
         <v>2.36</v>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>2.33</v>
@@ -1556,7 +1556,7 @@
         <v>5.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
         <v>3.68</v>
@@ -1565,10 +1565,10 @@
         <v>1.21</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
         <v>2.26</v>
@@ -1577,7 +1577,7 @@
         <v>1.57</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
         <v>1.89</v>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
         <v>3.25</v>
@@ -1767,10 +1767,10 @@
         <v>1.35</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W13" t="n">
         <v>1.79</v>
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.1</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.94</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Y14" t="n">
         <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="X16" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2144,49 +2144,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,49 +1134,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,55 +1336,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC9" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1446,22 +1446,22 @@
         <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="P10" t="n">
         <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.55</v>
+        <v>7.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="U10" t="n">
         <v>2.35</v>
@@ -1482,10 +1482,10 @@
         <v>2.21</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC10" s="3" t="n">
         <v>45971.4375</v>
@@ -1547,13 +1547,13 @@
         <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.53</v>
+        <v>5.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
@@ -1577,7 +1577,7 @@
         <v>1.57</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
         <v>1.89</v>
@@ -1660,7 +1660,7 @@
         <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="T12" t="n">
         <v>1.51</v>
@@ -1669,7 +1669,7 @@
         <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.48</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,49 +1740,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="T13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.18</v>
+        <v>3.13</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="X14" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1942,49 +1942,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="M15" t="n">
-        <v>3.58</v>
+        <v>3.41</v>
       </c>
       <c r="N15" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>4.39</v>
       </c>
       <c r="P15" t="n">
         <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
         <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="V15" t="n">
         <v>1.88</v>
       </c>
       <c r="W15" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X15" t="n">
         <v>1.98</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AA15" t="n">
         <v>2.37</v>
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.45</v>
+        <v>3.93</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
         <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="U16" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>1.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2144,16 +2144,16 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
         <v>1.9</v>
@@ -2165,16 +2165,16 @@
         <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="T17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
         <v>2.06</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,55 +1235,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AC8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,55 +1336,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,49 +1740,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.45</v>
+        <v>3.13</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="X13" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,49 +1841,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.13</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,49 +2043,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.93</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2144,49 +2144,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>3.93</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="X17" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,55 +528,85 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -679,7 +709,25 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>45971.33333333334</v>
       </c>
     </row>
@@ -780,7 +828,25 @@
       <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -881,7 +947,25 @@
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -982,7 +1066,25 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45971.375</v>
       </c>
     </row>
@@ -1083,7 +1185,25 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>45971.38541666666</v>
       </c>
     </row>
@@ -1184,7 +1304,25 @@
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1256,36 +1394,54 @@
         <v>1.58</v>
       </c>
       <c r="S8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.68</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1.21</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
+        <v>9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.51</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AB8" t="n">
         <v>1.44</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AC8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2.18</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AF8" t="n">
         <v>1.61</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AG8" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AH8" t="n">
         <v>1.68</v>
       </c>
-      <c r="AA8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1386,7 +1542,25 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>45971.41666666666</v>
       </c>
     </row>
@@ -1458,36 +1632,54 @@
         <v>1.52</v>
       </c>
       <c r="S10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.42</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>1.24</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA10" t="n">
         <v>2.35</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AB10" t="n">
         <v>1.52</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AC10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.36</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AF10" t="n">
         <v>1.5</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AG10" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AH10" t="n">
         <v>2.21</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC10" s="3" t="n">
+      <c r="AI10" s="3" t="n">
         <v>45971.4375</v>
       </c>
     </row>
@@ -1559,36 +1751,54 @@
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.68</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>1.21</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.64</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AB11" t="n">
         <v>1.4</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AC11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.26</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AF11" t="n">
         <v>1.57</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AG11" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AH11" t="n">
         <v>1.89</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="3" t="n">
+      <c r="AI11" s="3" t="n">
         <v>45971.5625</v>
       </c>
     </row>
@@ -1660,36 +1870,54 @@
         <v>1.26</v>
       </c>
       <c r="S12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.29</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>1.51</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.57</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AB12" t="n">
         <v>2.25</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AC12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.48</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AF12" t="n">
         <v>2.35</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AG12" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AH12" t="n">
         <v>1.43</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="3" t="n">
+      <c r="AI12" s="3" t="n">
         <v>45971.625</v>
       </c>
     </row>
@@ -1761,36 +1989,54 @@
         <v>1.43</v>
       </c>
       <c r="S13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.04</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1.33</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.98</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AB13" t="n">
         <v>1.77</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AC13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.83</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AF13" t="n">
         <v>1.97</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AG13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AH13" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="3" t="n">
+      <c r="AI13" s="3" t="n">
         <v>45971.6875</v>
       </c>
     </row>
@@ -1862,36 +2108,54 @@
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.89</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1.36</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.1</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AB14" t="n">
         <v>1.65</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AC14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.7</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AF14" t="n">
         <v>1.88</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AG14" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AH14" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="n">
+      <c r="AI14" s="3" t="n">
         <v>45971.6875</v>
       </c>
     </row>
@@ -1963,36 +2227,54 @@
         <v>1.38</v>
       </c>
       <c r="S15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.66</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>1.41</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.82</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AB15" t="n">
         <v>1.88</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AC15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.78</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AF15" t="n">
         <v>1.98</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AH15" t="n">
         <v>1.26</v>
       </c>
-      <c r="AA15" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC15" s="3" t="n">
+      <c r="AI15" s="3" t="n">
         <v>45971.70833333334</v>
       </c>
     </row>
@@ -2064,36 +2346,54 @@
         <v>1.52</v>
       </c>
       <c r="S16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.42</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>1.26</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.4</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AB16" t="n">
         <v>1.48</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AC16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2.06</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AF16" t="n">
         <v>1.68</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AH16" t="n">
         <v>1.61</v>
       </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="3" t="n">
+      <c r="AI16" s="3" t="n">
         <v>45971.79166666666</v>
       </c>
     </row>
@@ -2165,36 +2465,54 @@
         <v>1.44</v>
       </c>
       <c r="S17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.05</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>1.32</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.1</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AB17" t="n">
         <v>1.65</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AC17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.96</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AF17" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AG17" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AH17" t="n">
         <v>1.79</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="3" t="n">
+      <c r="AI17" s="3" t="n">
         <v>45971.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1382,31 +1382,31 @@
         <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
         <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>1.11</v>
@@ -1424,22 +1424,22 @@
         <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="AD8" t="n">
         <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AF8" t="n">
         <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1620,25 +1620,25 @@
         <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="P10" t="n">
         <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.1</v>
+        <v>7.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
         <v>8.9</v>
@@ -1650,10 +1650,10 @@
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AA10" t="n">
         <v>2.35</v>
@@ -1668,10 +1668,10 @@
         <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
         <v>1.23</v>
@@ -1739,7 +1739,7 @@
         <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="P11" t="n">
         <v>1.88</v>
@@ -1766,7 +1766,7 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" t="n">
         <v>1.52</v>
@@ -1781,7 +1781,7 @@
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.13</v>
@@ -1888,7 +1888,7 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
         <v>4.3</v>
@@ -1900,16 +1900,16 @@
         <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
         <v>1.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AG12" t="n">
         <v>1.21</v>
@@ -1977,13 +1977,13 @@
         <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.13</v>
+        <v>3.53</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
@@ -2019,16 +2019,16 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AD13" t="n">
         <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
         <v>1.33</v>
@@ -2096,25 +2096,25 @@
         <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.45</v>
+        <v>4.34</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
         <v>7.5</v>
@@ -2126,10 +2126,10 @@
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
         <v>2.1</v>
@@ -2147,13 +2147,13 @@
         <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
         <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45971.6875</v>
@@ -2215,31 +2215,31 @@
         <v>1.79</v>
       </c>
       <c r="O15" t="n">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="P15" t="n">
         <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
         <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="U15" t="n">
         <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2248,7 +2248,7 @@
         <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
         <v>1.82</v>
@@ -2260,19 +2260,19 @@
         <v>3.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45971.70833333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.93</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45971.79166666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.93</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45971.79166666666</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N2" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45971.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q3" t="n">
         <v>4.33</v>
       </c>
-      <c r="N3" t="n">
-        <v>8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45971.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45971.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>7</v>
-      </c>
-      <c r="N5" t="n">
-        <v>17</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45971.375</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45971.38541666666</v>
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1614,10 +1614,10 @@
         <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
         <v>2.19</v>
@@ -1632,7 +1632,7 @@
         <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
         <v>3.34</v>
@@ -1647,7 +1647,7 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
         <v>1.41</v>
@@ -1656,7 +1656,7 @@
         <v>2.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AB10" t="n">
         <v>1.52</v>
@@ -1668,10 +1668,10 @@
         <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
         <v>1.23</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.3</v>
+        <v>5.53</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
@@ -1760,31 +1760,31 @@
         <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
         <v>2.26</v>
@@ -1793,10 +1793,10 @@
         <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45971.5625</v>
@@ -1861,16 +1861,16 @@
         <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>2.29</v>
@@ -1879,31 +1879,31 @@
         <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
         <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
         <v>1.48</v>
@@ -1912,10 +1912,10 @@
         <v>2.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45971.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.26</v>
+        <v>2.76</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.53</v>
+        <v>3.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.02</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45971.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="O14" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.34</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45971.6875</v>
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="O15" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
         <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="T15" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
         <v>6.2</v>
@@ -2248,31 +2248,31 @@
         <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>3.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
         <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45971.70833333334</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="M2" t="n">
-        <v>3.56</v>
+        <v>3.37</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="O2" t="n">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>5.4</v>
+        <v>5.15</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45971.33333333334</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>2.75</v>
@@ -823,10 +823,10 @@
         <v>2.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
         <v>4.8</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,61 +897,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.3</v>
+        <v>8.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="n">
         <v>2.1</v>
@@ -960,10 +960,10 @@
         <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45971.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.199999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.1</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH5" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45971.375</v>
@@ -1147,61 +1147,61 @@
         <v>1.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.1</v>
+        <v>7.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
         <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45971.38541666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1614,31 +1614,31 @@
         <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.55</v>
+        <v>7.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V10" t="n">
         <v>8.9</v>
@@ -1647,16 +1647,16 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
         <v>1.52</v>
@@ -1674,7 +1674,7 @@
         <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
         <v>2.21</v>
@@ -1858,64 +1858,64 @@
         <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
         <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T12" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AC12" t="n">
         <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45971.625</v>
@@ -1971,37 +1971,37 @@
         <v>2.08</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
@@ -2013,28 +2013,28 @@
         <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
         <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45971.6875</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
         <v>2.98</v>
       </c>
       <c r="N14" t="n">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U14" t="n">
         <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
         <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
         <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45971.6875</v>
@@ -2325,52 +2325,52 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.97</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
         <v>1.65</v>
@@ -2379,19 +2379,19 @@
         <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45971.79166666666</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
         <v>1.52</v>
@@ -2468,7 +2468,7 @@
         <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
         <v>1.26</v>
@@ -2477,37 +2477,37 @@
         <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AC17" t="n">
         <v>4.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
         <v>1.61</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,61 +897,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.4</v>
+        <v>11.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="n">
         <v>2.1</v>
@@ -960,10 +960,10 @@
         <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45971.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,61 +1016,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.3</v>
+        <v>8.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
         <v>2.1</v>
@@ -1079,10 +1079,10 @@
         <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45971.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>7.17</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V8" t="n">
         <v>6.6</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
         <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
         <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.53</v>
+        <v>5.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="T11" t="n">
         <v>3.68</v>
@@ -1760,25 +1760,25 @@
         <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
         <v>5.2</v>
@@ -1787,10 +1787,10 @@
         <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
         <v>1.23</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>4.1</v>
@@ -1894,16 +1894,16 @@
         <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
         <v>1.62</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -2132,10 +2132,10 @@
         <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>3.78</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="N15" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="O15" t="n">
         <v>4.2</v>
@@ -2224,22 +2224,22 @@
         <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>6.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2251,10 +2251,10 @@
         <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
         <v>3.15</v>
@@ -2269,7 +2269,7 @@
         <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
         <v>1.24</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>2.67</v>
+        <v>3.05</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45971.79166666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V17" t="n">
-        <v>10</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45971.79166666666</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -668,22 +668,22 @@
         <v>2.73</v>
       </c>
       <c r="O2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
         <v>3.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="U2" t="n">
         <v>1.5</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.07</v>
+        <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.14</v>
+        <v>5.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>9.5</v>
+        <v>3.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.84</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.62</v>
+        <v>3.85</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45971.375</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.3</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
         <v>1.17</v>
@@ -921,10 +921,10 @@
         <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
         <v>4</v>
@@ -933,37 +933,37 @@
         <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
         <v>1.73</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45971.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.75</v>
+        <v>2.77</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>2.59</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45971.375</v>
@@ -1144,64 +1144,64 @@
         <v>9.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P6" t="n">
-        <v>2.73</v>
+        <v>2.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.75</v>
+        <v>7.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45971.38541666666</v>
@@ -1263,19 +1263,19 @@
         <v>4.15</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="P7" t="n">
         <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="R7" t="n">
         <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
         <v>3.6</v>
@@ -1290,7 +1290,7 @@
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
         <v>1.48</v>
@@ -1317,7 +1317,7 @@
         <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
         <v>1.7</v>
@@ -1382,25 +1382,25 @@
         <v>5.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="P8" t="n">
         <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.9</v>
+        <v>6.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
         <v>6.6</v>
@@ -1409,7 +1409,7 @@
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.25</v>
@@ -1424,22 +1424,22 @@
         <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
         <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1620,28 +1620,28 @@
         <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="T10" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
         <v>1.24</v>
       </c>
       <c r="V10" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
@@ -1650,10 +1650,10 @@
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="AA10" t="n">
         <v>2.35</v>
@@ -1662,22 +1662,22 @@
         <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
         <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45971.4375</v>
@@ -1739,19 +1739,19 @@
         <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.95</v>
+        <v>4.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="T11" t="n">
         <v>3.68</v>
@@ -1763,7 +1763,7 @@
         <v>10.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>1.05</v>
@@ -1787,16 +1787,16 @@
         <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
         <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45971.5625</v>
@@ -1858,25 +1858,25 @@
         <v>2.16</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
@@ -1888,10 +1888,10 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
         <v>1.57</v>
@@ -1912,10 +1912,10 @@
         <v>2.19</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45971.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.41</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45971.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
         <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45971.6875</v>
@@ -2215,13 +2215,13 @@
         <v>1.79</v>
       </c>
       <c r="O15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
         <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
@@ -2230,16 +2230,16 @@
         <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2260,13 +2260,13 @@
         <v>3.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG15" t="n">
         <v>1.31</v>
@@ -2334,16 +2334,16 @@
         <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
         <v>2.34</v>
@@ -2376,19 +2376,19 @@
         <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
         <v>1.61</v>
@@ -2453,7 +2453,7 @@
         <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="P17" t="n">
         <v>1.97</v>
@@ -2471,22 +2471,22 @@
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA17" t="n">
         <v>2.1</v>
@@ -2495,22 +2495,22 @@
         <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
         <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45971.79166666666</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -642,57 +642,57 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="M2" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N2" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="O2" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T2" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -701,31 +701,31 @@
         <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45971.33333333334</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>8.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
         <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45971.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC4" t="n">
         <v>4.4</v>
       </c>
-      <c r="N4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45971.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.77</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.1</v>
+        <v>10.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.41</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="W5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.04</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>4.55</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45971.375</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.25</v>
       </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="T6" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>5.05</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45971.38541666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>3.68</v>
       </c>
       <c r="O8" t="n">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.92</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.4</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.08</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AF8" t="n">
         <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1730,25 +1730,25 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="M11" t="n">
         <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>4.82</v>
       </c>
       <c r="O11" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="P11" t="n">
         <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.68</v>
+        <v>4.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
         <v>2.29</v>
@@ -1769,34 +1769,34 @@
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
         <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45971.5625</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.94</v>
+        <v>3.44</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="O12" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -1873,46 +1873,46 @@
         <v>3.08</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
         <v>1.24</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
         <v>3.1</v>
@@ -1983,25 +1983,25 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
         <v>2.47</v>
       </c>
       <c r="T13" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
         <v>1.08</v>
@@ -2010,31 +2010,31 @@
         <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.06</v>
+        <v>2.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
         <v>1.41</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45971.6875</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -752,66 +752,66 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.5</v>
+        <v>10.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
         <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
         <v>4.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
@@ -820,31 +820,31 @@
         <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
         <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45971.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,99 +871,99 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.25</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>2.85</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>2.36</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>2.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="W4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.05</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>4.05</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45971.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.52</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.25</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.22</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AH5" t="n">
-        <v>4.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45971.375</v>
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45971.41666666666</v>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1488,17 +1488,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="O9" t="n">
         <v>2.11</v>
@@ -1537,10 +1537,10 @@
         <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
         <v>2.97</v>
@@ -1597,17 +1597,17 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1623,37 +1623,37 @@
         <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.9</v>
+        <v>6.09</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="AA10" t="n">
         <v>2.35</v>
@@ -1662,22 +1662,22 @@
         <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>5.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45971.4375</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
         <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.82</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>2.59</v>
@@ -1769,13 +1769,13 @@
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AG12" t="n">
         <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45971.625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.66</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.8</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.47</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45971.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="M14" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.96</v>
+        <v>3.62</v>
       </c>
       <c r="R14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.36</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z14" t="n">
-        <v>3.16</v>
+        <v>2.72</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45971.6875</v>
@@ -2215,40 +2215,40 @@
         <v>1.79</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>4.39</v>
       </c>
       <c r="P15" t="n">
         <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="T15" t="n">
         <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="AA15" t="n">
         <v>1.82</v>
@@ -2260,19 +2260,19 @@
         <v>3.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45971.70833333334</v>
@@ -2343,10 +2343,10 @@
         <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
         <v>3.4</v>
@@ -2358,7 +2358,7 @@
         <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1.1</v>
@@ -2388,7 +2388,7 @@
         <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
         <v>1.61</v>
@@ -2453,13 +2453,13 @@
         <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
         <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
@@ -2471,10 +2471,10 @@
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
@@ -2483,10 +2483,10 @@
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
         <v>2.1</v>
@@ -2495,22 +2495,22 @@
         <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
         <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
         <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45971.79166666666</v>

--- a/jogos_2025-11-10.xlsx
+++ b/jogos_2025-11-10.xlsx
@@ -752,25 +752,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.25</v>
+        <v>8.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
         <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
         <v>4.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
@@ -820,31 +820,31 @@
         <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
         <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45971.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,99 +871,99 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
+      <c r="R4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.14</v>
       </c>
-      <c r="M4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>12</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.7</v>
       </c>
-      <c r="V4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.05</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45971.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.25</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.85</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>10.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.52</v>
+        <v>5.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.45</v>
+        <v>2.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>4.55</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45971.375</v>
@@ -1713,90 +1713,90 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="M11" t="n">
         <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>3.74</v>
       </c>
       <c r="O11" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
         <v>4.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="T11" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>10.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45971.5625</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2206,70 +2206,70 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="M15" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>4.39</v>
+        <v>3.82</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
         <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>3.15</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
         <v>1.25</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.24</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>4.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>5</v>
+        <v>3.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45971.79166666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="M17" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>4.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.53</v>
       </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3</v>
-      </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45971.79166666666</v>
